--- a/inflows_ny_dwelling_98_25.xlsx
+++ b/inflows_ny_dwelling_98_25.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/TEP4290-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A197274E-1B43-C84E-A7E0-80F44EF66910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E5AB4F-F037-EC4B-B072-CB563BC5794F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BYGV02" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Landstal for fuldført byggeri (ikke korrigeret for forsinkelser) efter byggesagstype, enhed, anvendelse og tid</t>
   </si>
@@ -131,6 +144,33 @@
   </si>
   <si>
     <t>Enhed: antall bygninger</t>
+  </si>
+  <si>
+    <t>Ratio Parcelhus</t>
+  </si>
+  <si>
+    <t>Ratio Rekke</t>
+  </si>
+  <si>
+    <t>Ratio Etage</t>
+  </si>
+  <si>
+    <t>Mean ratio Parcel</t>
+  </si>
+  <si>
+    <t>Mean ratio Rekke</t>
+  </si>
+  <si>
+    <t>Mean ratio Etage</t>
+  </si>
+  <si>
+    <t>Mean ratio Stuehus</t>
+  </si>
+  <si>
+    <t>Ratio Stuehus</t>
+  </si>
+  <si>
+    <t>Sum Boliger</t>
   </si>
 </sst>
 </file>
@@ -186,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -199,6 +239,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -968,8 +1009,629 @@
         <v>11448</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="160" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8">
+        <f>SUM(D4:D7)</f>
+        <v>13819</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ref="E8:AE8" si="0">SUM(E4:E7)</f>
+        <v>12595</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>12246</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>12918</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>14141</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>18446</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>20492</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>21253</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>23028</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>26643</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>21892</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>14656</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>7990</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>9496</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>11722</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>11345</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>11373</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>10856</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>15001</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>19228</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>22244</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>27223</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>31227</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>29020</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="0"/>
+        <v>33150</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="0"/>
+        <v>31592</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="0"/>
+        <v>23075</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="0"/>
+        <v>21110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9">
+        <f>D4/$D$8</f>
+        <v>1.6860843765829654E-2</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ref="E9:H9" si="1">E4/E8</f>
+        <v>1.8658197697499008E-2</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>1.8699983668136536E-2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>1.8346493265211334E-2</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>1.5628314829219999E-2</v>
+      </c>
+      <c r="I9">
+        <f t="shared" ref="I9" si="2">I4/I8</f>
+        <v>1.5938414832484007E-2</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9" si="3">J4/J8</f>
+        <v>1.5664649619363653E-2</v>
+      </c>
+      <c r="K9">
+        <f t="shared" ref="K9:L9" si="4">K4/K8</f>
+        <v>1.2986401919728979E-2</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="4"/>
+        <v>1.3896126454750739E-2</v>
+      </c>
+      <c r="M9">
+        <f t="shared" ref="M9" si="5">M4/M8</f>
+        <v>1.4825657771272004E-2</v>
+      </c>
+      <c r="N9">
+        <f t="shared" ref="N9" si="6">N4/N8</f>
+        <v>2.0007308605883428E-2</v>
+      </c>
+      <c r="O9">
+        <f t="shared" ref="O9:P9" si="7">O4/O8</f>
+        <v>3.356986899563319E-2</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="7"/>
+        <v>4.7058823529411764E-2</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q9" si="8">Q4/Q8</f>
+        <v>3.211878685762426E-2</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R9" si="9">R4/R8</f>
+        <v>2.4313257123357787E-2</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S9:T9" si="10">S4/S8</f>
+        <v>2.3622741295724989E-2</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="10"/>
+        <v>2.0926756352765322E-2</v>
+      </c>
+      <c r="U9">
+        <f t="shared" ref="U9" si="11">U4/U8</f>
+        <v>2.9200442151805454E-2</v>
+      </c>
+      <c r="V9">
+        <f t="shared" ref="V9" si="12">V4/V8</f>
+        <v>1.779881341243917E-2</v>
+      </c>
+      <c r="W9">
+        <f t="shared" ref="W9" si="13">W4/W8</f>
+        <v>1.1961722488038277E-2</v>
+      </c>
+      <c r="X9">
+        <f>X4/X8</f>
+        <v>9.2609242941916921E-3</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" ref="Y9" si="14">Y4/Y8</f>
+        <v>6.5018550490394149E-3</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" ref="Z9" si="15">Z4/Z8</f>
+        <v>6.0844781759374902E-3</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" ref="AA9" si="16">AA4/AA8</f>
+        <v>6.9951757408683668E-3</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" ref="AB9" si="17">AB4/AB8</f>
+        <v>7.4208144796380094E-3</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC9" si="18">AC4/AC8</f>
+        <v>6.7738668017219552E-3</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD9" si="19">AD4/AD8</f>
+        <v>7.453954496208017E-3</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" ref="AE9" si="20">AE4/AE8</f>
+        <v>8.5741354808147804E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ref="D10:E12" si="21">D5/$D$8</f>
+        <v>0.4594399015847746</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="21"/>
+        <v>0.43867139445690717</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ref="F10:AE10" si="22">F5/$D$8</f>
+        <v>0.35429481149142483</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="22"/>
+        <v>0.34213763658730734</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="22"/>
+        <v>0.32194804255011217</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="22"/>
+        <v>0.37028728562124613</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="22"/>
+        <v>0.42036326796439683</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="22"/>
+        <v>0.50915406324625512</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="22"/>
+        <v>0.60727983211520375</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="22"/>
+        <v>0.66509877704609599</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="22"/>
+        <v>0.63723858455749327</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="22"/>
+        <v>0.43548737245820973</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="22"/>
+        <v>0.29242347492582677</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="22"/>
+        <v>0.32310586873145669</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="22"/>
+        <v>0.27541790288732904</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="22"/>
+        <v>0.26072798321152035</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="22"/>
+        <v>0.27621390838700338</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="22"/>
+        <v>0.27990447934003909</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="22"/>
+        <v>0.33707214704392502</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="22"/>
+        <v>0.36782690498588899</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="22"/>
+        <v>0.3647152471235256</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="22"/>
+        <v>0.38989796656776904</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="22"/>
+        <v>0.42260655619075188</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="22"/>
+        <v>0.44091468268326217</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="22"/>
+        <v>0.52196251537737892</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="22"/>
+        <v>0.3729647586656053</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="22"/>
+        <v>0.23156523626890513</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="22"/>
+        <v>0.25971488530284392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="21"/>
+        <v>0.22454591504450394</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="21"/>
+        <v>0.26195817352919892</v>
+      </c>
+      <c r="F11">
+        <f t="shared" ref="F11:AE11" si="23">F6/$D$8</f>
+        <v>0.25710977639481875</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="23"/>
+        <v>0.30154135610391491</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="23"/>
+        <v>0.34727549026702365</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="23"/>
+        <v>0.52029814024169618</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="23"/>
+        <v>0.51942977060568785</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="23"/>
+        <v>0.47203126130689632</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="23"/>
+        <v>0.46132136912945942</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="23"/>
+        <v>0.49518778493378679</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="23"/>
+        <v>0.46305810840147621</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="23"/>
+        <v>0.24965627035241333</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="23"/>
+        <v>9.1612996598885596E-2</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="23"/>
+        <v>0.154207974527824</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="23"/>
+        <v>0.18633765106013458</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="23"/>
+        <v>0.17367392720167885</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="23"/>
+        <v>0.19002822201317027</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="23"/>
+        <v>0.20377740791663651</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="23"/>
+        <v>0.22469064331717201</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="23"/>
+        <v>0.28229249583906219</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="23"/>
+        <v>0.34213763658730734</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="23"/>
+        <v>0.40806136478761124</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="23"/>
+        <v>0.46175555394746365</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="23"/>
+        <v>0.52283088501338737</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="23"/>
+        <v>0.56292061654244152</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="23"/>
+        <v>0.57869599826326068</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="23"/>
+        <v>0.46877487517186484</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="23"/>
+        <v>0.42636949128012158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="21"/>
+        <v>0.29915333960489182</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="21"/>
+        <v>0.19379115710253997</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ref="F12:AE12" si="24">F7/$D$8</f>
+        <v>0.25819523843982922</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="24"/>
+        <v>0.27397062016064838</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="24"/>
+        <v>0.3380852449526015</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="24"/>
+        <v>0.422968376872422</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="24"/>
+        <v>0.51986395542369201</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="24"/>
+        <v>0.5367971633258557</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="24"/>
+        <v>0.57464360662855485</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="24"/>
+        <v>0.73912728851581155</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="24"/>
+        <v>0.45220348795137127</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="24"/>
+        <v>0.33982198422461829</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="24"/>
+        <v>0.16694406252261379</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="24"/>
+        <v>0.18778493378681527</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="24"/>
+        <v>0.36587307330487012</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="24"/>
+        <v>0.36717562775888268</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="24"/>
+        <v>0.33953252767928216</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="24"/>
+        <v>0.27896374556769665</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="24"/>
+        <v>0.50445039438454298</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="24"/>
+        <v>0.72465446124900501</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="24"/>
+        <v>0.88790795281858315</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="24"/>
+        <v>1.1592010999348723</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="24"/>
+        <v>1.3616035892611622</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="24"/>
+        <v>1.1215717490411752</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="24"/>
+        <v>1.2961864100151965</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="24"/>
+        <v>1.3189811129604168</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="24"/>
+        <v>0.95701570301758454</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="24"/>
+        <v>0.82842463275200806</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14">
+        <f>AVERAGE(D9:AE9)</f>
+        <v>1.7183886041235687E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:D17" si="25">AVERAGE(D10:AE10)</f>
+        <v>0.39208698169187345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="25"/>
+        <v>0.35184218415638929</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="25"/>
+        <v>0.60053187640205519</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="160" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>35</v>
       </c>
     </row>

--- a/inflows_ny_dwelling_98_25.xlsx
+++ b/inflows_ny_dwelling_98_25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E5AB4F-F037-EC4B-B072-CB563BC5794F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99B7CD1-A50D-9E46-954A-32AAE8109266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -240,6 +240,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1598,7 +1599,7 @@
       <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="7">
         <f>AVERAGE(D9:AE9)</f>
         <v>1.7183886041235687E-2</v>
       </c>

--- a/inflows_ny_dwelling_98_25.xlsx
+++ b/inflows_ny_dwelling_98_25.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99B7CD1-A50D-9E46-954A-32AAE8109266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8AC1A9-6484-014E-8124-867236672059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -240,7 +240,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1249,116 +1248,116 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <f t="shared" ref="D10:E12" si="21">D5/$D$8</f>
+        <f t="shared" ref="D10:D12" si="21">D5/$D$8</f>
         <v>0.4594399015847746</v>
       </c>
       <c r="E10">
-        <f t="shared" si="21"/>
-        <v>0.43867139445690717</v>
+        <f>E5/$E$8</f>
+        <v>0.48130210400952761</v>
       </c>
       <c r="F10">
-        <f t="shared" ref="F10:AE10" si="22">F5/$D$8</f>
-        <v>0.35429481149142483</v>
+        <f>F5/$F$8</f>
+        <v>0.39980401763841256</v>
       </c>
       <c r="G10">
-        <f t="shared" si="22"/>
-        <v>0.34213763658730734</v>
+        <f>G5/$G$8</f>
+        <v>0.36600092893636788</v>
       </c>
       <c r="H10">
-        <f t="shared" si="22"/>
-        <v>0.32194804255011217</v>
+        <f>H5/$H$8</f>
+        <v>0.31461707092850577</v>
       </c>
       <c r="I10">
-        <f t="shared" si="22"/>
-        <v>0.37028728562124613</v>
+        <f>I5/$I$8</f>
+        <v>0.27740431529870974</v>
       </c>
       <c r="J10">
-        <f t="shared" si="22"/>
-        <v>0.42036326796439683</v>
+        <f>J5/$J$8</f>
+        <v>0.28347647862580522</v>
       </c>
       <c r="K10">
-        <f t="shared" si="22"/>
-        <v>0.50915406324625512</v>
+        <f>K5/$K$8</f>
+        <v>0.33105914459135183</v>
       </c>
       <c r="L10">
-        <f t="shared" si="22"/>
-        <v>0.60727983211520375</v>
+        <f>L5/$L$8</f>
+        <v>0.36442591627583809</v>
       </c>
       <c r="M10">
-        <f t="shared" si="22"/>
-        <v>0.66509877704609599</v>
+        <f>M5/$M$8</f>
+        <v>0.34496865968547086</v>
       </c>
       <c r="N10">
-        <f t="shared" si="22"/>
-        <v>0.63723858455749327</v>
+        <f>N5/$N$8</f>
+        <v>0.40224739630915402</v>
       </c>
       <c r="O10">
-        <f t="shared" si="22"/>
-        <v>0.43548737245820973</v>
+        <f>O5/$O$8</f>
+        <v>0.41061681222707425</v>
       </c>
       <c r="P10">
-        <f t="shared" si="22"/>
-        <v>0.29242347492582677</v>
+        <f>P5/$P$8</f>
+        <v>0.50575719649561957</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="22"/>
-        <v>0.32310586873145669</v>
+        <f>Q5/$Q$8</f>
+        <v>0.47019797809604041</v>
       </c>
       <c r="R10">
-        <f t="shared" si="22"/>
-        <v>0.27541790288732904</v>
+        <f>R5/$R$8</f>
+        <v>0.32468861968947277</v>
       </c>
       <c r="S10">
-        <f t="shared" si="22"/>
-        <v>0.26072798321152035</v>
+        <f>S5/$S$8</f>
+        <v>0.31758483913618335</v>
       </c>
       <c r="T10">
-        <f t="shared" si="22"/>
-        <v>0.27621390838700338</v>
+        <f>T5/$T$8</f>
+        <v>0.33561944957355139</v>
       </c>
       <c r="U10">
-        <f t="shared" si="22"/>
-        <v>0.27990447934003909</v>
+        <f>U5/$U$8</f>
+        <v>0.3563006632277082</v>
       </c>
       <c r="V10">
-        <f t="shared" si="22"/>
-        <v>0.33707214704392502</v>
+        <f>V5/$V$8</f>
+        <v>0.31051263249116723</v>
       </c>
       <c r="W10">
-        <f t="shared" si="22"/>
-        <v>0.36782690498588899</v>
+        <f>W5/$W$8</f>
+        <v>0.26435406698564595</v>
       </c>
       <c r="X10">
-        <f t="shared" si="22"/>
-        <v>0.3647152471235256</v>
+        <f>X5/$X$8</f>
+        <v>0.22657795360546665</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="22"/>
-        <v>0.38989796656776904</v>
+        <f>Y5/$Y$8</f>
+        <v>0.19792087573008119</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="22"/>
-        <v>0.42260655619075188</v>
+        <f>Z5/$Z$8</f>
+        <v>0.18701764498671022</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="22"/>
-        <v>0.44091468268326217</v>
+        <f>AA5/$AA$8</f>
+        <v>0.20995864920744314</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="22"/>
-        <v>0.52196251537737892</v>
+        <f>AB5/$AB$8</f>
+        <v>0.21758672699849171</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="22"/>
-        <v>0.3729647586656053</v>
+        <f>AC5/$AC$8</f>
+        <v>0.163142567738668</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="22"/>
-        <v>0.23156523626890513</v>
+        <f>AD5/$AD$8</f>
+        <v>0.13867822318526543</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="22"/>
-        <v>0.25971488530284392</v>
+        <f>AE5/$AE$8</f>
+        <v>0.1700142112742776</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
@@ -1370,112 +1369,112 @@
         <v>0.22454591504450394</v>
       </c>
       <c r="E11">
-        <f t="shared" si="21"/>
-        <v>0.26195817352919892</v>
+        <f t="shared" ref="E11:E12" si="22">E6/$E$8</f>
+        <v>0.28741564112743151</v>
       </c>
       <c r="F11">
-        <f t="shared" ref="F11:AE11" si="23">F6/$D$8</f>
-        <v>0.25710977639481875</v>
+        <f t="shared" ref="F11:F12" si="23">F6/$F$8</f>
+        <v>0.29013555446676464</v>
       </c>
       <c r="G11">
-        <f t="shared" si="23"/>
-        <v>0.30154135610391491</v>
+        <f t="shared" ref="G11:G12" si="24">G6/$G$8</f>
+        <v>0.32257315373896889</v>
       </c>
       <c r="H11">
-        <f t="shared" si="23"/>
-        <v>0.34727549026702365</v>
+        <f t="shared" ref="H11:H12" si="25">H6/$H$8</f>
+        <v>0.33936779577116188</v>
       </c>
       <c r="I11">
-        <f t="shared" si="23"/>
-        <v>0.52029814024169618</v>
+        <f t="shared" ref="I11:I12" si="26">I6/$I$8</f>
+        <v>0.3897864035563266</v>
       </c>
       <c r="J11">
-        <f t="shared" si="23"/>
-        <v>0.51942977060568785</v>
+        <f t="shared" ref="J11:J12" si="27">J6/$J$8</f>
+        <v>0.3502830372828421</v>
       </c>
       <c r="K11">
-        <f t="shared" si="23"/>
-        <v>0.47203126130689632</v>
+        <f t="shared" ref="K11:K12" si="28">K6/$K$8</f>
+        <v>0.30692137580576861</v>
       </c>
       <c r="L11">
-        <f t="shared" si="23"/>
-        <v>0.46132136912945942</v>
+        <f t="shared" ref="L11:L12" si="29">L6/$L$8</f>
+        <v>0.27683689421573737</v>
       </c>
       <c r="M11">
-        <f t="shared" si="23"/>
-        <v>0.49518778493378679</v>
+        <f t="shared" ref="M11:M12" si="30">M6/$M$8</f>
+        <v>0.25684044589573246</v>
       </c>
       <c r="N11">
-        <f t="shared" si="23"/>
-        <v>0.46305810840147621</v>
+        <f t="shared" ref="N11:N12" si="31">N6/$N$8</f>
+        <v>0.29229855655033804</v>
       </c>
       <c r="O11">
-        <f t="shared" si="23"/>
-        <v>0.24965627035241333</v>
+        <f t="shared" ref="O11:O12" si="32">O6/$O$8</f>
+        <v>0.23539847161572053</v>
       </c>
       <c r="P11">
-        <f t="shared" si="23"/>
-        <v>9.1612996598885596E-2</v>
+        <f t="shared" ref="P11:P12" si="33">P6/$P$8</f>
+        <v>0.15844806007509388</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="23"/>
-        <v>0.154207974527824</v>
+        <f t="shared" ref="Q11:Q12" si="34">Q6/$Q$8</f>
+        <v>0.22441027801179445</v>
       </c>
       <c r="R11">
-        <f t="shared" si="23"/>
-        <v>0.18633765106013458</v>
+        <f t="shared" ref="R11:R12" si="35">R6/$R$8</f>
+        <v>0.21967241085139055</v>
       </c>
       <c r="S11">
-        <f t="shared" si="23"/>
-        <v>0.17367392720167885</v>
+        <f t="shared" ref="S11:S12" si="36">S6/$S$8</f>
+        <v>0.2115469369766417</v>
       </c>
       <c r="T11">
-        <f t="shared" si="23"/>
-        <v>0.19002822201317027</v>
+        <f t="shared" ref="T11:T12" si="37">T6/$T$8</f>
+        <v>0.23089774026202409</v>
       </c>
       <c r="U11">
-        <f t="shared" si="23"/>
-        <v>0.20377740791663651</v>
+        <f t="shared" ref="U11:U12" si="38">U6/$U$8</f>
+        <v>0.25939572586588061</v>
       </c>
       <c r="V11">
-        <f t="shared" si="23"/>
-        <v>0.22469064331717201</v>
+        <f t="shared" ref="V11:V12" si="39">V6/$V$8</f>
+        <v>0.20698620091993866</v>
       </c>
       <c r="W11">
-        <f t="shared" si="23"/>
-        <v>0.28229249583906219</v>
+        <f t="shared" ref="W11:W12" si="40">W6/$W$8</f>
+        <v>0.20288121489494487</v>
       </c>
       <c r="X11">
-        <f t="shared" si="23"/>
-        <v>0.34213763658730734</v>
+        <f t="shared" ref="X11:X12" si="41">X6/$X$8</f>
+        <v>0.21255169933465204</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="23"/>
-        <v>0.40806136478761124</v>
+        <f t="shared" ref="Y11:Y12" si="42">Y6/$Y$8</f>
+        <v>0.2071410204606399</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="23"/>
-        <v>0.46175555394746365</v>
+        <f t="shared" ref="Z11:Z12" si="43">Z6/$Z$8</f>
+        <v>0.20434239600345855</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="23"/>
-        <v>0.52283088501338737</v>
+        <f t="shared" ref="AA11:AA12" si="44">AA6/$AA$8</f>
+        <v>0.24896623018607858</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="23"/>
-        <v>0.56292061654244152</v>
+        <f t="shared" ref="AB11:AB12" si="45">AB6/$AB$8</f>
+        <v>0.23466063348416288</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="23"/>
-        <v>0.57869599826326068</v>
+        <f t="shared" ref="AC11:AC12" si="46">AC6/$AC$8</f>
+        <v>0.25313370473537605</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="23"/>
-        <v>0.46877487517186484</v>
+        <f t="shared" ref="AD11:AD12" si="47">AD6/$AD$8</f>
+        <v>0.28073672806067174</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="23"/>
-        <v>0.42636949128012158</v>
+        <f t="shared" ref="AE11:AE12" si="48">AE6/$AE$8</f>
+        <v>0.27910942681193746</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
@@ -1487,119 +1486,119 @@
         <v>0.29915333960489182</v>
       </c>
       <c r="E12">
-        <f t="shared" si="21"/>
-        <v>0.19379115710253997</v>
+        <f t="shared" si="22"/>
+        <v>0.21262405716554189</v>
       </c>
       <c r="F12">
-        <f t="shared" ref="F12:AE12" si="24">F7/$D$8</f>
-        <v>0.25819523843982922</v>
+        <f t="shared" si="23"/>
+        <v>0.29136044422668628</v>
       </c>
       <c r="G12">
         <f t="shared" si="24"/>
-        <v>0.27397062016064838</v>
+        <v>0.29307942405945192</v>
       </c>
       <c r="H12">
-        <f t="shared" si="24"/>
-        <v>0.3380852449526015</v>
+        <f t="shared" si="25"/>
+        <v>0.33038681847111234</v>
       </c>
       <c r="I12">
-        <f t="shared" si="24"/>
-        <v>0.422968376872422</v>
+        <f t="shared" si="26"/>
+        <v>0.31687086631247968</v>
       </c>
       <c r="J12">
-        <f t="shared" si="24"/>
-        <v>0.51986395542369201</v>
+        <f t="shared" si="27"/>
+        <v>0.35057583447198909</v>
       </c>
       <c r="K12">
-        <f t="shared" si="24"/>
-        <v>0.5367971633258557</v>
+        <f t="shared" si="28"/>
+        <v>0.34903307768315062</v>
       </c>
       <c r="L12">
-        <f t="shared" si="24"/>
-        <v>0.57464360662855485</v>
+        <f t="shared" si="29"/>
+        <v>0.34484106305367379</v>
       </c>
       <c r="M12">
-        <f t="shared" si="24"/>
-        <v>0.73912728851581155</v>
+        <f t="shared" si="30"/>
+        <v>0.3833652366475247</v>
       </c>
       <c r="N12">
-        <f t="shared" si="24"/>
-        <v>0.45220348795137127</v>
+        <f t="shared" si="31"/>
+        <v>0.28544673853462454</v>
       </c>
       <c r="O12">
-        <f t="shared" si="24"/>
-        <v>0.33982198422461829</v>
+        <f t="shared" si="32"/>
+        <v>0.32041484716157204</v>
       </c>
       <c r="P12">
-        <f t="shared" si="24"/>
-        <v>0.16694406252261379</v>
+        <f t="shared" si="33"/>
+        <v>0.28873591989987485</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="24"/>
-        <v>0.18778493378681527</v>
+        <f t="shared" si="34"/>
+        <v>0.27327295703454085</v>
       </c>
       <c r="R12">
-        <f t="shared" si="24"/>
-        <v>0.36587307330487012</v>
+        <f t="shared" si="35"/>
+        <v>0.43132571233577888</v>
       </c>
       <c r="S12">
-        <f t="shared" si="24"/>
-        <v>0.36717562775888268</v>
+        <f t="shared" si="36"/>
+        <v>0.44724548259144997</v>
       </c>
       <c r="T12">
-        <f t="shared" si="24"/>
-        <v>0.33953252767928216</v>
+        <f t="shared" si="37"/>
+        <v>0.41255605381165922</v>
       </c>
       <c r="U12">
-        <f t="shared" si="24"/>
-        <v>0.27896374556769665</v>
+        <f t="shared" si="38"/>
+        <v>0.35510316875460574</v>
       </c>
       <c r="V12">
-        <f t="shared" si="24"/>
-        <v>0.50445039438454298</v>
+        <f t="shared" si="39"/>
+        <v>0.46470235317645492</v>
       </c>
       <c r="W12">
-        <f t="shared" si="24"/>
-        <v>0.72465446124900501</v>
+        <f t="shared" si="40"/>
+        <v>0.52080299563137089</v>
       </c>
       <c r="X12">
-        <f t="shared" si="24"/>
-        <v>0.88790795281858315</v>
+        <f t="shared" si="41"/>
+        <v>0.55160942276568958</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="24"/>
-        <v>1.1592010999348723</v>
+        <f t="shared" si="42"/>
+        <v>0.58843624876023948</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="24"/>
-        <v>1.3616035892611622</v>
+        <f t="shared" si="43"/>
+        <v>0.60255548083389376</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="24"/>
-        <v>1.1215717490411752</v>
+        <f t="shared" si="44"/>
+        <v>0.53407994486560995</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="24"/>
-        <v>1.2961864100151965</v>
+        <f t="shared" si="45"/>
+        <v>0.54033182503770738</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="24"/>
-        <v>1.3189811129604168</v>
+        <f t="shared" si="46"/>
+        <v>0.57694986072423393</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="24"/>
-        <v>0.95701570301758454</v>
+        <f t="shared" si="47"/>
+        <v>0.5731310942578548</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="24"/>
-        <v>0.82842463275200806</v>
+        <f t="shared" si="48"/>
+        <v>0.5423022264329701</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14">
         <f>AVERAGE(D9:AE9)</f>
         <v>1.7183886041235687E-2</v>
       </c>
@@ -1609,8 +1608,8 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <f t="shared" ref="D15:D17" si="25">AVERAGE(D10:AE10)</f>
-        <v>0.39208698169187345</v>
+        <f t="shared" ref="D15:D17" si="49">AVERAGE(D10:AE10)</f>
+        <v>0.31540268016188522</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
@@ -1618,8 +1617,8 @@
         <v>41</v>
       </c>
       <c r="D16">
-        <f t="shared" si="25"/>
-        <v>0.35184218415638929</v>
+        <f t="shared" si="49"/>
+        <v>0.25740298757164226</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -1627,8 +1626,8 @@
         <v>42</v>
       </c>
       <c r="D17">
-        <f t="shared" si="25"/>
-        <v>0.60053187640205519</v>
+        <f t="shared" si="49"/>
+        <v>0.41001044622523691</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="160" x14ac:dyDescent="0.2">
